--- a/internship_application_form_templates/032_internship_portal_access_form--internship_application_form_templates.xlsx
+++ b/internship_application_form_templates/032_internship_portal_access_form--internship_application_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'once'}</t>
+          <t>once</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'once'}</t>
+          <t>once</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'multiple'}</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'multiple'}</t>
+          <t>multiple</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'biweekly'}</t>
+          <t>biweekly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'biweekly'}</t>
+          <t>biweekly</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'triweekly'}</t>
+          <t>triweekly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'triweekly'}</t>
+          <t>triweekly</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'internship'}</t>
+          <t>internship</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'internship'}</t>
+          <t>internship</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'research'}</t>
+          <t>research</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'research'}</t>
+          <t>research</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'project'}</t>
+          <t>project</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'project'}</t>
+          <t>project</t>
         </is>
       </c>
     </row>
